--- a/各ファイルの役割.xlsx
+++ b/各ファイルの役割.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harum\tsumitate-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBD05A8E-9740-4E3E-BE98-4586E662523C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E002074-DF1E-4388-9804-96FAE3338FDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3C580CBF-04C4-4F8B-80B8-FCB043677C6C}"/>
   </bookViews>
@@ -624,11 +624,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B06A49D7-90EE-4E5D-9686-3251C57F1291}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="19.3984375" customWidth="1"/>
-    <col min="2" max="2" width="24.09765625" customWidth="1"/>
+    <col min="2" max="2" width="35.69921875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="85.8984375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
